--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.65106015856304</v>
+        <v>2.705797275766495</v>
       </c>
       <c r="D2" t="n">
-        <v>16.89314845005011</v>
+        <v>2.745136623133142</v>
       </c>
       <c r="E2" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F2" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.11432476603391</v>
+        <v>3.106077774480511</v>
       </c>
       <c r="D3" t="n">
-        <v>23.75537131434066</v>
+        <v>3.860247838580357</v>
       </c>
       <c r="E3" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F3" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.52901227245274</v>
+        <v>1.71096449427357</v>
       </c>
       <c r="D4" t="n">
-        <v>43.36766007974148</v>
+        <v>7.04724476295799</v>
       </c>
       <c r="E4" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F4" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.58740078733108</v>
+        <v>5.457952627941301</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58641853564565</v>
+        <v>5.132793012042418</v>
       </c>
       <c r="E5" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F5" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.87742154970078</v>
+        <v>1.930081001826377</v>
       </c>
       <c r="D6" t="n">
-        <v>12.1855705926696</v>
+        <v>1.98015522130881</v>
       </c>
       <c r="E6" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F6" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.14817593854371</v>
+        <v>4.411578590013352</v>
       </c>
       <c r="D7" t="n">
-        <v>48.81953810706516</v>
+        <v>7.933174942398089</v>
       </c>
       <c r="E7" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F7" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.71340672699969</v>
+        <v>1.41592859313745</v>
       </c>
       <c r="D8" t="n">
-        <v>58.63151303682734</v>
+        <v>9.527620868484442</v>
       </c>
       <c r="E8" t="n">
-        <v>8.526301309388366</v>
+        <v>1.38552396277561</v>
       </c>
       <c r="F8" t="n">
-        <v>16.00127605902095</v>
+        <v>2.600207359590904</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
